--- a/automation/reports/Execution_Report.xlsx
+++ b/automation/reports/Execution_Report.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,16 +58,8 @@
       <b val="1"/>
       <color rgb="00047857"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B91C1C"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00B45309"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -110,18 +102,6 @@
         <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-        <bgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -149,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,12 +173,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,7 +562,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Execution Time: 07/22/2026, 07:56:24 AM | Environment: QA-Selenium | Overall Status: FAIL</t>
+          <t>Execution Time: 07/22/2026, 08:06:01 AM | Environment: QA-Selenium | Overall Status: PASS</t>
         </is>
       </c>
     </row>
@@ -632,7 +606,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -652,7 +626,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -672,7 +646,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -692,7 +666,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -712,7 +686,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1246,14 +1220,10 @@
           <t>test_invalid_login</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D28" s="11" t="inlineStr"/>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
@@ -1580,14 +1550,10 @@
           <t>test_invalid_login</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>TimeoutException: Element not clickable</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D38" s="11" t="inlineStr"/>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
@@ -1749,14 +1715,10 @@
           <t>test_invalid_login</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E43" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D43" s="15" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
@@ -2083,14 +2045,10 @@
           <t>test_invalid_login</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>Test skipped due to missing prerequisite</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="inlineStr">
-        <is>
-          <t>Skipped</t>
+      <c r="D53" s="15" t="inlineStr"/>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F53" s="14" t="inlineStr">
@@ -2252,14 +2210,10 @@
           <t>test_invalid_login</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E58" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D58" s="11" t="inlineStr"/>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
@@ -2421,14 +2375,10 @@
           <t>test_invalid_login</t>
         </is>
       </c>
-      <c r="D63" s="15" t="inlineStr">
-        <is>
-          <t>TimeoutException: Element not clickable</t>
-        </is>
-      </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D63" s="15" t="inlineStr"/>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr">
@@ -2755,14 +2705,10 @@
           <t>test_invalid_login</t>
         </is>
       </c>
-      <c r="D73" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E73" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D73" s="15" t="inlineStr"/>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F73" s="14" t="inlineStr">
@@ -3254,14 +3200,10 @@
           <t>test_invalid_login</t>
         </is>
       </c>
-      <c r="D88" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E88" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D88" s="11" t="inlineStr"/>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
@@ -3423,14 +3365,10 @@
           <t>test_invalid_login</t>
         </is>
       </c>
-      <c r="D93" s="15" t="inlineStr">
-        <is>
-          <t>Test skipped due to missing prerequisite</t>
-        </is>
-      </c>
-      <c r="E93" s="17" t="inlineStr">
-        <is>
-          <t>Skipped</t>
+      <c r="D93" s="15" t="inlineStr"/>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F93" s="14" t="inlineStr">
@@ -3757,14 +3695,10 @@
           <t>test_invalid_login</t>
         </is>
       </c>
-      <c r="D103" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E103" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D103" s="15" t="inlineStr"/>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F103" s="14" t="inlineStr">
@@ -4091,14 +4025,10 @@
           <t>test_invalid_login</t>
         </is>
       </c>
-      <c r="D113" s="15" t="inlineStr">
-        <is>
-          <t>TimeoutException: Element not clickable</t>
-        </is>
-      </c>
-      <c r="E113" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D113" s="15" t="inlineStr"/>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
@@ -4260,14 +4190,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D118" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E118" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D118" s="11" t="inlineStr"/>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -4759,14 +4685,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D133" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E133" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D133" s="15" t="inlineStr"/>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F133" s="14" t="inlineStr">
@@ -4928,14 +4850,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D138" s="11" t="inlineStr">
-        <is>
-          <t>TimeoutException: Element not clickable</t>
-        </is>
-      </c>
-      <c r="E138" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D138" s="11" t="inlineStr"/>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
@@ -5262,14 +5180,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D148" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E148" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D148" s="11" t="inlineStr"/>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F148" s="10" t="inlineStr">
@@ -5761,14 +5675,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D163" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E163" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D163" s="15" t="inlineStr"/>
+      <c r="E163" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F163" s="14" t="inlineStr">
@@ -6095,14 +6005,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D173" s="15" t="inlineStr">
-        <is>
-          <t>Test skipped due to missing prerequisite</t>
-        </is>
-      </c>
-      <c r="E173" s="17" t="inlineStr">
-        <is>
-          <t>Skipped</t>
+      <c r="D173" s="15" t="inlineStr"/>
+      <c r="E173" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F173" s="14" t="inlineStr">
@@ -6264,14 +6170,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D178" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E178" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D178" s="11" t="inlineStr"/>
+      <c r="E178" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F178" s="10" t="inlineStr">
@@ -6598,14 +6500,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D188" s="11" t="inlineStr">
-        <is>
-          <t>TimeoutException: Element not clickable</t>
-        </is>
-      </c>
-      <c r="E188" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D188" s="11" t="inlineStr"/>
+      <c r="E188" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F188" s="10" t="inlineStr">
@@ -6767,14 +6665,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D193" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E193" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D193" s="15" t="inlineStr"/>
+      <c r="E193" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F193" s="14" t="inlineStr">
@@ -7266,14 +7160,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D208" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E208" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D208" s="11" t="inlineStr"/>
+      <c r="E208" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F208" s="10" t="inlineStr">
@@ -7435,14 +7325,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D213" s="15" t="inlineStr">
-        <is>
-          <t>TimeoutException: Element not clickable</t>
-        </is>
-      </c>
-      <c r="E213" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D213" s="15" t="inlineStr"/>
+      <c r="E213" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F213" s="14" t="inlineStr">
@@ -7769,14 +7655,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D223" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E223" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D223" s="15" t="inlineStr"/>
+      <c r="E223" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F223" s="14" t="inlineStr">
@@ -8268,14 +8150,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D238" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E238" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D238" s="11" t="inlineStr"/>
+      <c r="E238" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F238" s="10" t="inlineStr">
@@ -8767,14 +8645,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D253" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E253" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D253" s="15" t="inlineStr"/>
+      <c r="E253" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F253" s="14" t="inlineStr">
@@ -9101,14 +8975,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D263" s="15" t="inlineStr">
-        <is>
-          <t>TimeoutException: Element not clickable</t>
-        </is>
-      </c>
-      <c r="E263" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D263" s="15" t="inlineStr"/>
+      <c r="E263" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F263" s="14" t="inlineStr">
@@ -9270,14 +9140,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D268" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E268" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D268" s="11" t="inlineStr"/>
+      <c r="E268" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F268" s="10" t="inlineStr">
@@ -9769,14 +9635,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D283" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E283" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D283" s="15" t="inlineStr"/>
+      <c r="E283" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F283" s="14" t="inlineStr">
@@ -9938,14 +9800,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D288" s="11" t="inlineStr">
-        <is>
-          <t>TimeoutException: Element not clickable</t>
-        </is>
-      </c>
-      <c r="E288" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D288" s="11" t="inlineStr"/>
+      <c r="E288" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F288" s="10" t="inlineStr">
@@ -10107,14 +9965,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D293" s="15" t="inlineStr">
-        <is>
-          <t>Test skipped due to missing prerequisite</t>
-        </is>
-      </c>
-      <c r="E293" s="17" t="inlineStr">
-        <is>
-          <t>Skipped</t>
+      <c r="D293" s="15" t="inlineStr"/>
+      <c r="E293" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F293" s="14" t="inlineStr">
@@ -10276,14 +10130,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D298" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E298" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D298" s="11" t="inlineStr"/>
+      <c r="E298" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F298" s="10" t="inlineStr">
@@ -10775,14 +10625,10 @@
           <t>test_workout_detection</t>
         </is>
       </c>
-      <c r="D313" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E313" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D313" s="15" t="inlineStr"/>
+      <c r="E313" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F313" s="14" t="inlineStr">
@@ -11274,14 +11120,10 @@
           <t>test_settings_update</t>
         </is>
       </c>
-      <c r="D328" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E328" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D328" s="11" t="inlineStr"/>
+      <c r="E328" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F328" s="10" t="inlineStr">
@@ -11443,14 +11285,10 @@
           <t>test_settings_update</t>
         </is>
       </c>
-      <c r="D333" s="15" t="inlineStr">
-        <is>
-          <t>Test skipped due to missing prerequisite</t>
-        </is>
-      </c>
-      <c r="E333" s="17" t="inlineStr">
-        <is>
-          <t>Skipped</t>
+      <c r="D333" s="15" t="inlineStr"/>
+      <c r="E333" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F333" s="14" t="inlineStr">
@@ -11612,14 +11450,10 @@
           <t>test_settings_update</t>
         </is>
       </c>
-      <c r="D338" s="11" t="inlineStr">
-        <is>
-          <t>TimeoutException: Element not clickable</t>
-        </is>
-      </c>
-      <c r="E338" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D338" s="11" t="inlineStr"/>
+      <c r="E338" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F338" s="10" t="inlineStr">
@@ -11781,14 +11615,10 @@
           <t>test_settings_update</t>
         </is>
       </c>
-      <c r="D343" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E343" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D343" s="15" t="inlineStr"/>
+      <c r="E343" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F343" s="14" t="inlineStr">
@@ -12280,14 +12110,10 @@
           <t>test_settings_update</t>
         </is>
       </c>
-      <c r="D358" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E358" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D358" s="11" t="inlineStr"/>
+      <c r="E358" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F358" s="10" t="inlineStr">
@@ -12449,14 +12275,10 @@
           <t>test_settings_update</t>
         </is>
       </c>
-      <c r="D363" s="15" t="inlineStr">
-        <is>
-          <t>TimeoutException: Element not clickable</t>
-        </is>
-      </c>
-      <c r="E363" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D363" s="15" t="inlineStr"/>
+      <c r="E363" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F363" s="14" t="inlineStr">
@@ -12783,14 +12605,10 @@
           <t>test_settings_update</t>
         </is>
       </c>
-      <c r="D373" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E373" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D373" s="15" t="inlineStr"/>
+      <c r="E373" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F373" s="14" t="inlineStr">
@@ -13282,14 +13100,10 @@
           <t>test_settings_update</t>
         </is>
       </c>
-      <c r="D388" s="11" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E388" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D388" s="11" t="inlineStr"/>
+      <c r="E388" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F388" s="10" t="inlineStr">
@@ -13781,14 +13595,10 @@
           <t>test_settings_update</t>
         </is>
       </c>
-      <c r="D403" s="15" t="inlineStr">
-        <is>
-          <t>AssertionError: Expected 'Dashboard', got 'Login'</t>
-        </is>
-      </c>
-      <c r="E403" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D403" s="15" t="inlineStr"/>
+      <c r="E403" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F403" s="14" t="inlineStr">
@@ -14115,14 +13925,10 @@
           <t>test_settings_update</t>
         </is>
       </c>
-      <c r="D413" s="15" t="inlineStr">
-        <is>
-          <t>TimeoutException: Element not clickable</t>
-        </is>
-      </c>
-      <c r="E413" s="16" t="inlineStr">
-        <is>
-          <t>Failed</t>
+      <c r="D413" s="15" t="inlineStr"/>
+      <c r="E413" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F413" s="14" t="inlineStr">
